--- a/data/trans_dic/P32B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,11</t>
+          <t>0,6; 3,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,66</t>
+          <t>1,28; 4,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,16</t>
+          <t>1,24; 5,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,92</t>
+          <t>2,72; 9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,25</t>
+          <t>0,32; 2,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,5</t>
+          <t>1,0; 3,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,27</t>
+          <t>1,11; 4,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,39</t>
+          <t>2,49; 7,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,28</t>
+          <t>0,32; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,05</t>
+          <t>2,08; 4,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,84</t>
+          <t>1,21; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,74</t>
+          <t>0,64; 2,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,66</t>
+          <t>0,54; 2,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,15</t>
+          <t>0,37; 2,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,09</t>
+          <t>0,53; 2,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,68</t>
+          <t>0,43; 2,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,45</t>
+          <t>0,55; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,17</t>
+          <t>1,78; 3,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,26</t>
+          <t>1,1; 2,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,1</t>
+          <t>0,71; 2,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,55</t>
+          <t>1,15; 5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,11</t>
+          <t>0,98; 4,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,5</t>
+          <t>0,83; 3,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,71</t>
+          <t>0,33; 3,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,23</t>
+          <t>0,56; 2,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,91</t>
+          <t>0,19; 2,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,52</t>
+          <t>0,7; 3,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,11</t>
+          <t>0,88; 3,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,85</t>
+          <t>0,83; 2,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,49; 1,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,79</t>
+          <t>2,16; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,85</t>
+          <t>1,53; 2,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,89</t>
+          <t>1,29; 2,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,82</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,3; 1,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,8</t>
+          <t>0,51; 1,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,29</t>
+          <t>0,57; 2,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,28</t>
+          <t>0,59; 1,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,81</t>
+          <t>1,65; 2,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,29</t>
+          <t>1,27; 2,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,41</t>
+          <t>1,15; 2,34</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2734; 14638</t>
+          <t>2845; 14610</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6758; 23851</t>
+          <t>6534; 23687</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4370; 18513</t>
+          <t>4464; 18229</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6553; 21692</t>
+          <t>6614; 22707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1936</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5531</t>
+          <t>0; 5512</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2814; 14346</t>
+          <t>2026; 13338</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7443; 25933</t>
+          <t>7428; 25042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5383; 21096</t>
+          <t>5492; 20060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7194; 22959</t>
+          <t>7745; 23237</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3363; 13546</t>
+          <t>3380; 14332</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26119; 48593</t>
+          <t>24905; 50290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15543; 35697</t>
+          <t>15195; 35882</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6529; 26928</t>
+          <t>6260; 24479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3139; 14162</t>
+          <t>2903; 14382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2873; 12773</t>
+          <t>2200; 13044</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3769; 15220</t>
+          <t>3818; 14662</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2712; 18998</t>
+          <t>3066; 19893</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8412; 23076</t>
+          <t>8713; 25004</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31454; 56872</t>
+          <t>31868; 57045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22323; 44800</t>
+          <t>21812; 44717</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12191; 35552</t>
+          <t>12070; 35478</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7190</t>
+          <t>0; 7406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3908; 18119</t>
+          <t>3750; 18275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3036; 15507</t>
+          <t>3691; 16304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2643; 12035</t>
+          <t>2848; 12300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6785</t>
+          <t>0; 6235</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2123</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>909; 7605</t>
+          <t>916; 8739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1365; 7929</t>
+          <t>1371; 7348</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1012; 10378</t>
+          <t>1018; 11019</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3731; 19368</t>
+          <t>3842; 17781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5718; 20469</t>
+          <t>5801; 20253</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5571; 16829</t>
+          <t>4886; 16188</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8534; 24749</t>
+          <t>9219; 24710</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44572; 77177</t>
+          <t>44069; 75223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31400; 56742</t>
+          <t>30571; 57869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20404; 45349</t>
+          <t>20197; 45275</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4061; 16261</t>
+          <t>4583; 18108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3043; 14437</t>
+          <t>3117; 14522</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6658; 20551</t>
+          <t>5860; 19904</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5711; 23348</t>
+          <t>5787; 22959</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15956; 35383</t>
+          <t>16469; 36675</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51484; 86561</t>
+          <t>51046; 84876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41558; 71759</t>
+          <t>39827; 70203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30561; 62497</t>
+          <t>29712; 60576</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32B-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,1</t>
+          <t>0,57; 3,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,63</t>
+          <t>1,35; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,08</t>
+          <t>1,37; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,33</t>
+          <t>2,84; 8,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,09</t>
+          <t>0,43; 2,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,38</t>
+          <t>1,06; 3,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,06</t>
+          <t>1,07; 3,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,48</t>
+          <t>2,31; 6,62</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,35</t>
+          <t>0,34; 1,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,2</t>
+          <t>2,28; 4,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,86</t>
+          <t>1,3; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,49</t>
+          <t>0,73; 2,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,7</t>
+          <t>0,6; 2,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,2</t>
+          <t>0,49; 2,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,02</t>
+          <t>0,52; 2,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,81</t>
+          <t>1,07; 4,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,57</t>
+          <t>0,52; 1,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,18</t>
+          <t>1,75; 3,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,26</t>
+          <t>1,13; 2,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,1</t>
+          <t>1,01; 2,6</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,6</t>
+          <t>1,16; 5,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,32</t>
+          <t>1,0; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,57</t>
+          <t>1,1; 4,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,11</t>
+          <t>0,33; 2,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,99</t>
+          <t>0,76; 3,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,02</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,23</t>
+          <t>0,6; 3,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,08</t>
+          <t>0,85; 3,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,74</t>
+          <t>1,3; 3,39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,31</t>
+          <t>0,45; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,69</t>
+          <t>2,18; 3,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,91</t>
+          <t>1,53; 2,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,88</t>
+          <t>1,49; 3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,02</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,38</t>
+          <t>0,3; 1,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,74</t>
+          <t>0,55; 1,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,25</t>
+          <t>1,15; 3,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,32</t>
+          <t>0,6; 1,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,75</t>
+          <t>1,58; 2,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,24</t>
+          <t>1,33; 2,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,34</t>
+          <t>1,57; 2,83</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13636</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2845; 14610</t>
+          <t>2702; 14310</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6534; 23687</t>
+          <t>6899; 25119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4464; 18229</t>
+          <t>4918; 18726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6614; 22707</t>
+          <t>7315; 21120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1529,37 +1529,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 5656</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026; 13338</t>
+          <t>2756; 14640</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7428; 25042</t>
+          <t>7875; 27143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5492; 20060</t>
+          <t>5266; 19584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7745; 23237</t>
+          <t>7675; 22036</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>26536</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3380; 14332</t>
+          <t>3599; 14643</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24905; 50290</t>
+          <t>27296; 50617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15195; 35882</t>
+          <t>16318; 36248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6260; 24479</t>
+          <t>7674; 28342</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2903; 14382</t>
+          <t>3181; 14935</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2200; 13044</t>
+          <t>2887; 12617</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3818; 14662</t>
+          <t>3783; 14544</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3066; 19893</t>
+          <t>5980; 23042</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8713; 25004</t>
+          <t>8313; 23574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31868; 57045</t>
+          <t>31382; 56170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21812; 44717</t>
+          <t>22468; 47010</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12070; 35478</t>
+          <t>16204; 41596</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>13338</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7406</t>
+          <t>0; 8027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3750; 18275</t>
+          <t>3792; 18293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3691; 16304</t>
+          <t>3769; 16937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2848; 12300</t>
+          <t>4043; 17273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 7108</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>916; 8739</t>
+          <t>921; 7895</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1371; 7348</t>
+          <t>2052; 10120</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1018; 11019</t>
+          <t>1023; 10361</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3842; 17781</t>
+          <t>3281; 18684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5801; 20253</t>
+          <t>5606; 20232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4886; 16188</t>
+          <t>8260; 21609</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9219; 24710</t>
+          <t>8433; 24419</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44069; 75223</t>
+          <t>44346; 79059</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30571; 57869</t>
+          <t>30500; 57343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20197; 45275</t>
+          <t>24933; 53057</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4583; 18108</t>
+          <t>4926; 17607</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3117; 14522</t>
+          <t>3102; 14773</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5860; 19904</t>
+          <t>6318; 19854</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5787; 22959</t>
+          <t>10368; 29635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16469; 36675</t>
+          <t>16605; 36431</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51046; 84876</t>
+          <t>48703; 83926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39827; 70203</t>
+          <t>41721; 69451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29712; 60576</t>
+          <t>40293; 72707</t>
         </is>
       </c>
     </row>
